--- a/Output/acct_profiling/account_profiling_summary.xlsx
+++ b/Output/acct_profiling/account_profiling_summary.xlsx
@@ -1594,7 +1594,7 @@
         <v>0.48</v>
       </c>
       <c r="AQ6" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AR6" t="b">
         <v>1</v>
@@ -1776,7 +1776,7 @@
         <v>0</v>
       </c>
       <c r="AQ7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AR7" t="b">
         <v>1</v>
@@ -1972,7 +1972,7 @@
         <v>0.87</v>
       </c>
       <c r="AQ8" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AR8" t="b">
         <v>1</v>
@@ -2156,7 +2156,7 @@
         <v>0</v>
       </c>
       <c r="AQ9" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AR9" t="b">
         <v>1</v>
@@ -2348,7 +2348,7 @@
         <v>0.85</v>
       </c>
       <c r="AQ10" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AR10" t="b">
         <v>1</v>
@@ -2540,7 +2540,7 @@
         <v>1.39</v>
       </c>
       <c r="AQ11" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AR11" t="b">
         <v>1</v>
@@ -2724,7 +2724,7 @@
         <v>0</v>
       </c>
       <c r="AQ12" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AR12" t="b">
         <v>1</v>
@@ -2908,7 +2908,7 @@
         <v>0</v>
       </c>
       <c r="AQ13" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AR13" t="b">
         <v>1</v>
@@ -3086,7 +3086,7 @@
         <v>0</v>
       </c>
       <c r="AQ14" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AR14" t="b">
         <v>1</v>
@@ -3270,7 +3270,7 @@
         <v>0</v>
       </c>
       <c r="AQ15" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AR15" t="b">
         <v>1</v>
@@ -3462,7 +3462,7 @@
         <v>1.72</v>
       </c>
       <c r="AQ16" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AR16" t="b">
         <v>1</v>
@@ -3646,7 +3646,7 @@
         <v>0</v>
       </c>
       <c r="AQ17" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AR17" t="b">
         <v>1</v>
@@ -3793,7 +3793,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B12"/>
+  <dimension ref="A1:B9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3821,27 +3821,27 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>1st Login HCM vs Order Can Tho</t>
+          <t>Missing Email</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>100</v>
+        <v>93.75</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Missing Email</t>
+          <t>Account Age &lt; 90 Days</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>93.75</v>
+        <v>87.5</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Account Age &lt; 90 Days</t>
+          <t>Extreme High Freq (&lt;30s Lag)</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -3851,17 +3851,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Extreme High Freq (&lt;30s Lag)</t>
+          <t>Incomplete Profile Name</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>87.5</v>
+        <v>75</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Pre-Reg Order Anomaly</t>
+          <t>WEB Access Channel</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -3871,50 +3871,20 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Incomplete Profile Name</t>
+          <t>Zero Order Completion</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>75</v>
+        <v>62.5</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>WEB Access Channel</t>
+          <t>Shared Device ID</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Zero Order Completion</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>62.5</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Corporate Account Flag</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>18.75</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Shared Device ID (Bot Farm)</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
         <v>18.75</v>
       </c>
     </row>

--- a/Output/acct_profiling/account_profiling_summary.xlsx
+++ b/Output/acct_profiling/account_profiling_summary.xlsx
@@ -9,7 +9,6 @@
   <sheets>
     <sheet name="Account_Profiles" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Age_Tier_Summary" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Risk_Indicator_Prevalence" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -415,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX17"/>
+  <dimension ref="A1:AY17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,6 +668,11 @@
           <t>hcm_login_cantho_target</t>
         </is>
       </c>
+      <c r="AY1" t="inlineStr">
+        <is>
+          <t>reg_year_month</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -821,7 +825,7 @@
       </c>
       <c r="AK2" t="inlineStr"/>
       <c r="AL2" t="n">
-        <v>1715</v>
+        <v>1716</v>
       </c>
       <c r="AM2" t="n">
         <v>2021</v>
@@ -860,6 +864,11 @@
       </c>
       <c r="AX2" t="b">
         <v>1</v>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>2021 Dec</t>
+        </is>
       </c>
     </row>
     <row r="3">
@@ -1005,7 +1014,7 @@
       </c>
       <c r="AK3" t="inlineStr"/>
       <c r="AL3" t="n">
-        <v>917</v>
+        <v>918</v>
       </c>
       <c r="AM3" t="n">
         <v>2024</v>
@@ -1044,6 +1053,11 @@
       </c>
       <c r="AX3" t="b">
         <v>1</v>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>2024 Mar</t>
+        </is>
       </c>
     </row>
     <row r="4">
@@ -1189,7 +1203,7 @@
       </c>
       <c r="AK4" t="inlineStr"/>
       <c r="AL4" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="AM4" t="n">
         <v>2026</v>
@@ -1228,6 +1242,11 @@
       </c>
       <c r="AX4" t="b">
         <v>1</v>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>2026 Jul</t>
+        </is>
       </c>
     </row>
     <row r="5">
@@ -1385,7 +1404,7 @@
         </is>
       </c>
       <c r="AL5" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="AM5" t="n">
         <v>2026</v>
@@ -1424,6 +1443,11 @@
       </c>
       <c r="AX5" t="b">
         <v>1</v>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>2026 Jul</t>
+        </is>
       </c>
     </row>
     <row r="6">
@@ -1577,7 +1601,7 @@
         </is>
       </c>
       <c r="AL6" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="AM6" t="n">
         <v>2026</v>
@@ -1616,6 +1640,11 @@
       </c>
       <c r="AX6" t="b">
         <v>1</v>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>2026 Jul</t>
+        </is>
       </c>
     </row>
     <row r="7">
@@ -1759,7 +1788,7 @@
       </c>
       <c r="AK7" t="inlineStr"/>
       <c r="AL7" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="AM7" t="n">
         <v>2026</v>
@@ -1798,6 +1827,11 @@
       </c>
       <c r="AX7" t="b">
         <v>1</v>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>2026 Jul</t>
+        </is>
       </c>
     </row>
     <row r="8">
@@ -1955,7 +1989,7 @@
         </is>
       </c>
       <c r="AL8" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="AM8" t="n">
         <v>2026</v>
@@ -1994,6 +2028,11 @@
       </c>
       <c r="AX8" t="b">
         <v>1</v>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>2026 Jul</t>
+        </is>
       </c>
     </row>
     <row r="9">
@@ -2139,7 +2178,7 @@
       </c>
       <c r="AK9" t="inlineStr"/>
       <c r="AL9" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="AM9" t="n">
         <v>2026</v>
@@ -2178,6 +2217,11 @@
       </c>
       <c r="AX9" t="b">
         <v>1</v>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>2026 Aug</t>
+        </is>
       </c>
     </row>
     <row r="10">
@@ -2331,7 +2375,7 @@
         </is>
       </c>
       <c r="AL10" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AM10" t="n">
         <v>2026</v>
@@ -2341,7 +2385,7 @@
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>&lt; 30 Days</t>
+          <t>30 - 90 Days</t>
         </is>
       </c>
       <c r="AP10" t="n">
@@ -2370,6 +2414,11 @@
       </c>
       <c r="AX10" t="b">
         <v>1</v>
+      </c>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t>2026 Aug</t>
+        </is>
       </c>
     </row>
     <row r="11">
@@ -2523,7 +2572,7 @@
         </is>
       </c>
       <c r="AL11" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AM11" t="n">
         <v>2026</v>
@@ -2562,6 +2611,11 @@
       </c>
       <c r="AX11" t="b">
         <v>1</v>
+      </c>
+      <c r="AY11" t="inlineStr">
+        <is>
+          <t>2026 Aug</t>
+        </is>
       </c>
     </row>
     <row r="12">
@@ -2707,7 +2761,7 @@
       </c>
       <c r="AK12" t="inlineStr"/>
       <c r="AL12" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AM12" t="n">
         <v>2026</v>
@@ -2746,6 +2800,11 @@
       </c>
       <c r="AX12" t="b">
         <v>1</v>
+      </c>
+      <c r="AY12" t="inlineStr">
+        <is>
+          <t>2026 Aug</t>
+        </is>
       </c>
     </row>
     <row r="13">
@@ -2891,7 +2950,7 @@
       </c>
       <c r="AK13" t="inlineStr"/>
       <c r="AL13" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AM13" t="n">
         <v>2026</v>
@@ -2930,6 +2989,11 @@
       </c>
       <c r="AX13" t="b">
         <v>1</v>
+      </c>
+      <c r="AY13" t="inlineStr">
+        <is>
+          <t>2026 Aug</t>
+        </is>
       </c>
     </row>
     <row r="14">
@@ -3069,7 +3133,7 @@
       </c>
       <c r="AK14" t="inlineStr"/>
       <c r="AL14" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AM14" t="n">
         <v>2026</v>
@@ -3108,6 +3172,11 @@
       </c>
       <c r="AX14" t="b">
         <v>1</v>
+      </c>
+      <c r="AY14" t="inlineStr">
+        <is>
+          <t>2026 Aug</t>
+        </is>
       </c>
     </row>
     <row r="15">
@@ -3253,7 +3322,7 @@
       </c>
       <c r="AK15" t="inlineStr"/>
       <c r="AL15" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AM15" t="n">
         <v>2026</v>
@@ -3292,6 +3361,11 @@
       </c>
       <c r="AX15" t="b">
         <v>1</v>
+      </c>
+      <c r="AY15" t="inlineStr">
+        <is>
+          <t>2026 Aug</t>
+        </is>
       </c>
     </row>
     <row r="16">
@@ -3445,7 +3519,7 @@
         </is>
       </c>
       <c r="AL16" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AM16" t="n">
         <v>2026</v>
@@ -3484,6 +3558,11 @@
       </c>
       <c r="AX16" t="b">
         <v>1</v>
+      </c>
+      <c r="AY16" t="inlineStr">
+        <is>
+          <t>2026 Aug</t>
+        </is>
       </c>
     </row>
     <row r="17">
@@ -3629,7 +3708,7 @@
       </c>
       <c r="AK17" t="inlineStr"/>
       <c r="AL17" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AM17" t="n">
         <v>2026</v>
@@ -3668,6 +3747,11 @@
       </c>
       <c r="AX17" t="b">
         <v>1</v>
+      </c>
+      <c r="AY17" t="inlineStr">
+        <is>
+          <t>2026 Aug</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -3723,19 +3807,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C2" t="n">
-        <v>786</v>
+        <v>669</v>
       </c>
       <c r="D2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E2" t="n">
-        <v>98.25</v>
+        <v>95.57142857142857</v>
       </c>
       <c r="F2" t="n">
-        <v>0.6361323155216284</v>
+        <v>0.5979073243647235</v>
       </c>
     </row>
     <row r="3">
@@ -3745,19 +3829,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C3" t="n">
-        <v>718</v>
+        <v>835</v>
       </c>
       <c r="D3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E3" t="n">
-        <v>119.6666666666667</v>
+        <v>119.2857142857143</v>
       </c>
       <c r="F3" t="n">
-        <v>0.4178272980501393</v>
+        <v>0.4790419161676647</v>
       </c>
     </row>
     <row r="4">
@@ -3780,112 +3864,6 @@
       </c>
       <c r="F4" t="n">
         <v>0</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:B9"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Indicator</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>Percentage</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Banned Status</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Missing Email</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>93.75</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Account Age &lt; 90 Days</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>87.5</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Extreme High Freq (&lt;30s Lag)</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>87.5</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Incomplete Profile Name</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>WEB Access Channel</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Zero Order Completion</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>62.5</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Shared Device ID</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>18.75</v>
       </c>
     </row>
   </sheetData>
